--- a/AAII_Financials/Yearly/CRZBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRZBY_YR_FIN.xlsx
@@ -1059,10 +1059,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4727000</v>
+        <v>190200</v>
       </c>
       <c r="E15" s="3">
-        <v>1587100</v>
+        <v>176000</v>
       </c>
       <c r="F15" s="3">
         <v>170200</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10164400</v>
+        <v>5627600</v>
       </c>
       <c r="E21" s="3">
-        <v>5559600</v>
+        <v>4148500</v>
       </c>
       <c r="F21" s="3">
         <v>3977000</v>
@@ -4090,10 +4090,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5032300</v>
+        <v>495500</v>
       </c>
       <c r="E83" s="3">
-        <v>1877000</v>
+        <v>465900</v>
       </c>
       <c r="F83" s="3">
         <v>481900</v>
